--- a/tables/new/balanced all/all_roc_auc.xlsx
+++ b/tables/new/balanced all/all_roc_auc.xlsx
@@ -425,36 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 1, 1)_ABROOD</t>
+          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>XGBoost(1, 1, 1, 1)_ABROOD</t>
+          <t>Logit(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Logit(1, 1, 0, 0)</t>
+          <t>XGBoost(1, 1, 0, 0)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost(1, 1, 0, 0)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Logit(1, 1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>XGBoost(1, 1, 1, 1)</t>
         </is>
@@ -467,21 +457,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9215139874432514</v>
+        <v>0.9392784268253678</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9392784268253678</v>
+        <v>0.9343032110837984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9343032110837984</v>
+        <v>0.938313899244086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.938313899244086</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.927794278979578</v>
-      </c>
-      <c r="G2" t="n">
         <v>0.9383659433002411</v>
       </c>
     </row>
@@ -492,21 +476,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6933506281300399</v>
+        <v>0.6838432645785586</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6838432645785586</v>
+        <v>0.6920366479925304</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6920366479925304</v>
+        <v>0.6525629191070368</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6525629191070368</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6972405780494016</v>
-      </c>
-      <c r="G3" t="n">
         <v>0.6554770393005687</v>
       </c>
     </row>
@@ -517,21 +495,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9948413539679174</v>
+        <v>0.986622853508586</v>
       </c>
       <c r="C4" t="n">
-        <v>0.986622853508586</v>
+        <v>0.9928968506348196</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9928968506348196</v>
+        <v>0.9908722587331872</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9908722587331872</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9943678891951098</v>
-      </c>
-      <c r="G4" t="n">
         <v>0.9926306739217488</v>
       </c>
     </row>
@@ -542,21 +514,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.72945912723576</v>
+        <v>0.7392421188513452</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7392421188513452</v>
+        <v>0.7317025621282121</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7317025621282121</v>
+        <v>0.7397194668397902</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7397194668397902</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.7285474605187668</v>
-      </c>
-      <c r="G5" t="n">
         <v>0.7365001987901481</v>
       </c>
     </row>
@@ -567,21 +533,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9220383166723628</v>
+        <v>0.938238885566188</v>
       </c>
       <c r="C6" t="n">
-        <v>0.938238885566188</v>
+        <v>0.9282136449077238</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9282136449077238</v>
+        <v>0.9365721654989748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9365721654989748</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9255580357142856</v>
-      </c>
-      <c r="G6" t="n">
         <v>0.9345535358282068</v>
       </c>
     </row>
@@ -592,21 +552,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9312026002166848</v>
+        <v>0.9585590465872156</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9585590465872156</v>
+        <v>0.9320151679306607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9320151679306607</v>
+        <v>0.9534127843987</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9534127843987</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9336403033586133</v>
-      </c>
-      <c r="G7" t="n">
         <v>0.9672264355362946</v>
       </c>
     </row>
@@ -617,21 +571,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7736571428571428</v>
+        <v>0.764647619047619</v>
       </c>
       <c r="C8" t="n">
-        <v>0.764647619047619</v>
+        <v>0.7779047619047619</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7779047619047619</v>
+        <v>0.784552380952381</v>
       </c>
       <c r="E8" t="n">
-        <v>0.784552380952381</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.7755428571428571</v>
-      </c>
-      <c r="G8" t="n">
         <v>0.7792571428571429</v>
       </c>
     </row>
@@ -642,21 +590,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8978247984826931</v>
+        <v>0.9000740872451398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9000740872451398</v>
+        <v>0.8808558558558559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8808558558558559</v>
+        <v>0.8657242769084875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8657242769084875</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8863916548127074</v>
-      </c>
-      <c r="G9" t="n">
         <v>0.8990457562825984</v>
       </c>
     </row>
@@ -667,21 +609,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7408061958366836</v>
+        <v>0.746286741713571</v>
       </c>
       <c r="C10" t="n">
-        <v>0.746286741713571</v>
+        <v>0.7488622911641205</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7488622911641205</v>
+        <v>0.7310442352363083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7310442352363083</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.7399532632002144</v>
-      </c>
-      <c r="G10" t="n">
         <v>0.7532616646564816</v>
       </c>
     </row>
@@ -692,21 +628,15 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.88646112824905</v>
+        <v>0.9742197448005094</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9742197448005094</v>
+        <v>0.8835088603565365</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8835088603565365</v>
+        <v>0.9702725184938152</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9702725184938152</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.888078073838831</v>
-      </c>
-      <c r="G11" t="n">
         <v>0.9670326269302288</v>
       </c>
     </row>
@@ -717,21 +647,15 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6626184714660215</v>
+        <v>0.627293809235733</v>
       </c>
       <c r="C12" t="n">
-        <v>0.627293809235733</v>
+        <v>0.673049001814882</v>
       </c>
       <c r="D12" t="n">
-        <v>0.673049001814882</v>
+        <v>0.593158903004638</v>
       </c>
       <c r="E12" t="n">
-        <v>0.593158903004638</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.6720004033071183</v>
-      </c>
-      <c r="G12" t="n">
         <v>0.6438898971566848</v>
       </c>
     </row>
@@ -742,21 +666,15 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6286792899408284</v>
+        <v>0.8504449704142012</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8504449704142012</v>
+        <v>0.6285562130177516</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6285562130177516</v>
+        <v>0.8570130177514794</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8570130177514794</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.6193751479289942</v>
-      </c>
-      <c r="G13" t="n">
         <v>0.8349349112426036</v>
       </c>
     </row>
@@ -767,21 +685,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8686397412778227</v>
+        <v>0.8565130745363303</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8565130745363303</v>
+        <v>0.869529854813285</v>
       </c>
       <c r="D14" t="n">
-        <v>0.869529854813285</v>
+        <v>0.8592384431773966</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8592384431773966</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8670858618169665</v>
-      </c>
-      <c r="G14" t="n">
         <v>0.8537092168996239</v>
       </c>
     </row>
@@ -792,21 +704,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.791524470899471</v>
+        <v>0.8775388558201058</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8775388558201058</v>
+        <v>0.7760896164021164</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7760896164021164</v>
+        <v>0.8638153108465608</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8638153108465608</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8150033068783069</v>
-      </c>
-      <c r="G15" t="n">
         <v>0.912323082010582</v>
       </c>
     </row>
@@ -817,21 +723,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9690544929727124</v>
+        <v>0.992368902472422</v>
       </c>
       <c r="C16" t="n">
-        <v>0.992368902472422</v>
+        <v>0.9878620175928664</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9878620175928664</v>
+        <v>0.9953746973829788</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9953746973829788</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9730059866136472</v>
-      </c>
-      <c r="G16" t="n">
         <v>0.984592357071653</v>
       </c>
     </row>
